--- a/ARM Functions/Ability Edits/Turboblaze.xlsx
+++ b/ARM Functions/Ability Edits/Turboblaze.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE57073E-361B-46AB-87C1-DCE675397F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0580200C-5124-4A2C-9393-19ACA721EE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Edited" sheetId="6" r:id="rId1"/>
     <sheet name="original" sheetId="12" r:id="rId2"/>
     <sheet name="Table of IDs" sheetId="11" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="1191">
   <si>
     <t>Address</t>
   </si>
@@ -3565,60 +3565,6 @@
     <t>Regenerator 0x6A</t>
   </si>
   <si>
-    <t>cmp r0, 0x0</t>
-  </si>
-  <si>
-    <t>mov r0, 0x2</t>
-  </si>
-  <si>
-    <t>check self</t>
-  </si>
-  <si>
-    <t>10402DE9</t>
-  </si>
-  <si>
-    <t>push {r4, lr}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bl 0x00087B58 </t>
-  </si>
-  <si>
-    <t>4900A0E3</t>
-  </si>
-  <si>
-    <t>mov r0, 0x49</t>
-  </si>
-  <si>
-    <t>Check if STAB</t>
-  </si>
-  <si>
-    <t>3900A0E3</t>
-  </si>
-  <si>
-    <t>mov r0, 0x39</t>
-  </si>
-  <si>
-    <t>1040BDE8</t>
-  </si>
-  <si>
-    <t>b 0x00082D44</t>
-  </si>
-  <si>
-    <t>Get type</t>
-  </si>
-  <si>
-    <t>mov r0, 0x12</t>
-  </si>
-  <si>
-    <t>bl 0x000001D8</t>
-  </si>
-  <si>
-    <t>1200A0E3</t>
-  </si>
-  <si>
-    <t>branching to previous pop from nearly-identical function to fit</t>
-  </si>
-  <si>
     <t>Turboblaze Call function</t>
   </si>
   <si>
@@ -3646,61 +3592,25 @@
     <t>000DA5D0</t>
   </si>
   <si>
-    <t>Fire-only Adaptability 0x54</t>
-  </si>
-  <si>
-    <t>cmp r0, 0x9</t>
-  </si>
-  <si>
-    <t>if STAB Adaptability boost</t>
-  </si>
-  <si>
-    <t>movne r1, 0x2000</t>
-  </si>
-  <si>
-    <t>moveq r1, 0x1800</t>
-  </si>
-  <si>
-    <t>if not STAB give it</t>
-  </si>
-  <si>
     <t>00101CE4</t>
   </si>
   <si>
-    <t>9817FEEB</t>
-  </si>
-  <si>
-    <t>0C00001A</t>
-  </si>
-  <si>
-    <t>9417FEEB</t>
-  </si>
-  <si>
-    <t>33F9FBEB</t>
-  </si>
-  <si>
-    <t>090050E3</t>
-  </si>
-  <si>
-    <t>0700001A</t>
-  </si>
-  <si>
-    <t>8F17FEEB</t>
-  </si>
-  <si>
-    <t>021AA013</t>
-  </si>
-  <si>
-    <t>061BA003</t>
-  </si>
-  <si>
-    <t>0404FEEA</t>
-  </si>
-  <si>
-    <t>1080BDE8</t>
-  </si>
-  <si>
     <t>000D3E18</t>
+  </si>
+  <si>
+    <t>b 0x001032EC</t>
+  </si>
+  <si>
+    <t>mov r0, 0x9</t>
+  </si>
+  <si>
+    <t>Fire-only Adaptability 0x5B</t>
+  </si>
+  <si>
+    <t>0900A0E3</t>
+  </si>
+  <si>
+    <t>7F0500EA</t>
   </si>
 </sst>
 </file>
@@ -3748,30 +3658,12 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3786,7 +3678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3808,13 +3700,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4149,7 +4034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="9.0703125" defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="8" customWidth="1"/>
@@ -4182,14 +4067,14 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="7" t="s">
-        <v>1193</v>
+        <v>1175</v>
       </c>
       <c r="B2" s="9"/>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>1220</v>
+        <v>1185</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
@@ -4256,7 +4141,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>1194</v>
+        <v>1176</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="12"/>
@@ -4264,7 +4149,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="8" t="s">
-        <v>1195</v>
+        <v>1177</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="12"/>
@@ -4272,308 +4157,60 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
-        <v>1196</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="8" t="s">
-        <v>1197</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
-        <v>1198</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="8" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="8" t="s">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1178</v>
+        <v>1189</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="8" t="str">
-        <f t="shared" ref="A23:A41" si="1">DEC2HEX(HEX2DEC(A22)+4,8)</f>
+        <f t="shared" ref="A23" si="1">DEC2HEX(HEX2DEC(A22)+4,8)</f>
         <v>00101CE8</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>852</v>
+        <v>1190</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>00101CEC</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>869</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>00101CF0</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>1209</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D25" s="13"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>00101CF4</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>854</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>846</v>
-      </c>
-      <c r="D26" s="13"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>00101CF8</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C27" s="13" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A41)</f>
-        <v>bne 0x00101D30</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>00101CFC</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D00</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D29" s="17"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D04</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>1190</v>
-      </c>
-      <c r="D30" s="17"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D08</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>1213</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D0C</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C32" s="17" t="str">
-        <f>C27</f>
-        <v>bne 0x00101D30</v>
-      </c>
-      <c r="D32" s="17"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D10</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>1182</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D14</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D34" s="15"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D18</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>855</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>1175</v>
-      </c>
-      <c r="D35" s="15"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D1C</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D20</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D24</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D28</v>
-      </c>
-      <c r="B39" s="8" t="s">
         <v>1186</v>
-      </c>
-      <c r="C39" s="8" t="str">
-        <f>SUBSTITUTE(C22,"push","pop")</f>
-        <v>pop {r4, lr}</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D2C</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>00101D30</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>1219</v>
-      </c>
-      <c r="C41" s="8" t="str">
-        <f>SUBSTITUTE(C39,"lr","pc")</f>
-        <v>pop {r4, pc}</v>
       </c>
     </row>
   </sheetData>
